--- a/output/pdf_financials_xlsx/FHYD.xlsx
+++ b/output/pdf_financials_xlsx/FHYD.xlsx
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.02958</v>
+        <v>-0.02958</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.052122</v>
+        <v>-0.052122</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.047881</v>
+        <v>-0.047881</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.047707</v>
+        <v>-0.047707</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-0.054962</v>
@@ -1569,22 +1569,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.02958</v>
+        <v>-0.02958</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.052122</v>
+        <v>-0.052122</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.047881</v>
+        <v>-0.047881</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.047707</v>
+        <v>-0.047707</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-0.054962</v>
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.02958</v>
+        <v>-0.02958</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.052122</v>
+        <v>-0.052122</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.047881</v>
+        <v>-0.047881</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.047707</v>
+        <v>-0.047707</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-0.054962</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-3.209217</v>
+        <v>3.209217</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-3.4122</v>
+        <v>3.4122</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2033,22 +2033,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.02958</v>
+        <v>-0.02958</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.052122</v>
+        <v>-0.052122</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.047881</v>
+        <v>-0.047881</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.047707</v>
+        <v>-0.047707</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.054962</v>
@@ -2149,22 +2149,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.02958</v>
+        <v>-0.02958</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.052122</v>
+        <v>-0.052122</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.047881</v>
+        <v>-0.047881</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.047707</v>
+        <v>-0.047707</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.054962</v>
@@ -2295,22 +2295,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -50140,16 +50140,16 @@
         </is>
       </c>
       <c r="G409" s="5" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="H409" s="5" t="n">
-        <v>0.052122</v>
+        <v>-0.052122</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>0.047881</v>
+        <v>-0.047881</v>
       </c>
       <c r="J409" s="5" t="n">
-        <v>0.047707</v>
+        <v>-0.047707</v>
       </c>
       <c r="K409" s="5" t="n">
         <v>-0.054962</v>
@@ -51186,10 +51186,10 @@
         </is>
       </c>
       <c r="F420" s="5" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="G420" s="5" t="n">
-        <v>0.068244</v>
+        <v>-0.068244</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
@@ -51999,10 +51999,10 @@
         </is>
       </c>
       <c r="E428" s="5" t="n">
-        <v>0.02958</v>
+        <v>-0.02958</v>
       </c>
       <c r="F428" s="5" t="n">
-        <v>0.192553</v>
+        <v>-0.192553</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FHYD.xlsx
+++ b/output/pdf_financials_xlsx/FHYD.xlsx
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002486</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>5.9e-05</v>
       </c>
     </row>
     <row r="13">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.02958</v>
+        <v>-0.027094</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.192553</v>
@@ -2081,7 +2081,7 @@
         <v>-10.909869</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-5.066816</v>
+        <v>-5.066875</v>
       </c>
     </row>
     <row r="28">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.02958</v>
+        <v>-0.027094</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.192553</v>
@@ -2197,7 +2197,7 @@
         <v>-10.909869</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.066816</v>
+        <v>-5.066875</v>
       </c>
     </row>
     <row r="30">
@@ -2448,71 +2448,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.333287</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.255947</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.220785</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.16235</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.110981</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.054102</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.013955</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.000885</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.000744</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.518819</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.262429</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0.334576</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.63738</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.599377</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.394816</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.087475</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.011507</v>
       </c>
     </row>
     <row r="35">
@@ -2596,71 +2580,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.333287</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.255947</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.220785</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.16235</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.110981</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.054102</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.013955</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.000885</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.000744</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.518819</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.262429</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0.334576</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.63738</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.599377</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.394816</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.087475</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.011507</v>
       </c>
     </row>
     <row r="37">
@@ -3455,13 +3423,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.255947</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.220785</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.16235</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -3504,19 +3472,19 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.668881</v>
+        <v>0.031501</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.706136</v>
+        <v>0.106759</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.536836</v>
+        <v>0.14202</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.374512</v>
+        <v>0.287037</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.138943</v>
+        <v>0.127436</v>
       </c>
     </row>
     <row r="49">
@@ -9509,7 +9477,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13713,7 +13681,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
@@ -16257,7 +16225,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -43130,7 +43098,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -43235,7 +43203,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -44718,7 +44686,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -51789,7 +51757,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E426" s="5" t="n">

--- a/output/pdf_financials_xlsx/FHYD.xlsx
+++ b/output/pdf_financials_xlsx/FHYD.xlsx
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.349173</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.362997</v>
@@ -17027,7 +17027,11 @@
           <t>Share capital – Note 4</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17126,7 +17130,11 @@
           <t>Contributed surplus – Note 4</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -17629,7 +17637,11 @@
           <t>Share capital - Notes 4 and 9</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.349173</v>
       </c>

--- a/output/pdf_financials_xlsx/FHYD.xlsx
+++ b/output/pdf_financials_xlsx/FHYD.xlsx
@@ -1611,13 +1611,13 @@
         <v>-8.868093999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-13.854429</v>
+        <v>-13.686518</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-10.909869</v>
+        <v>-10.736713</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-5.066816</v>
+        <v>-4.957047</v>
       </c>
     </row>
     <row r="21">
@@ -1669,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-0.167911</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-0.173156</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>-0.109769</v>
       </c>
     </row>
     <row r="22">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002833</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00547</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.004764</v>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.016462</v>
+        <v>-0.019295</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.074033</v>
+        <v>0.068563</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.033082</v>
@@ -7798,16 +7798,16 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.268859</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.114242</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.090916</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.310344</v>
       </c>
     </row>
     <row r="111">
@@ -18037,7 +18037,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -19223,7 +19227,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -33120,7 +33128,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -38890,7 +38902,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -39605,7 +39621,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E304" s="5" t="n">
         <v>-0.002833</v>
       </c>
@@ -43409,7 +43429,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -43506,7 +43530,11 @@
           <t>Net loss from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
